--- a/ig/DM-SEPTEMBRE-2026/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5558" uniqueCount="3804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5555" uniqueCount="3803">
   <si>
     <t>Property</t>
   </si>
@@ -115,7 +115,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1720</t>
+    <t>1719</t>
   </si>
   <si>
     <t>Code</t>
@@ -11401,25 +11401,22 @@
     <t>1715</t>
   </si>
   <si>
+    <t>Prise en charge médecine nucléaire pédiatrique (0 - 5 ans)</t>
+  </si>
+  <si>
     <t>1716</t>
   </si>
   <si>
-    <t>Prise en charge médecine nucléaire pédiatrique (0 - 5 ans)</t>
+    <t>Exploration diagnostique scintigraphique splénique ou hépatosplénique</t>
   </si>
   <si>
     <t>1717</t>
   </si>
   <si>
-    <t>Exploration diagnostique scintigraphique splénique ou hépatosplénique</t>
+    <t>Exploration diagnostique scintigraphique des glandes salivaires</t>
   </si>
   <si>
     <t>1718</t>
-  </si>
-  <si>
-    <t>Exploration diagnostique scintigraphique des glandes salivaires</t>
-  </si>
-  <si>
-    <t>1719</t>
   </si>
   <si>
     <t>Exploration diagnostique scintigraphique aux leucocytes marqués pour recherche d'infection</t>
@@ -11839,7 +11836,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1721"/>
+  <dimension ref="A1:D1720"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -33094,7 +33091,7 @@
         <v>3794</v>
       </c>
       <c r="C1716" t="s" s="2">
-        <v>3793</v>
+        <v>3795</v>
       </c>
       <c r="D1716" s="2"/>
     </row>
@@ -33103,10 +33100,10 @@
         <v>60</v>
       </c>
       <c r="B1717" t="s" s="2">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C1717" t="s" s="2">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="D1717" s="2"/>
     </row>
@@ -33115,10 +33112,10 @@
         <v>60</v>
       </c>
       <c r="B1718" t="s" s="2">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C1718" t="s" s="2">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="D1718" s="2"/>
     </row>
@@ -33127,10 +33124,10 @@
         <v>60</v>
       </c>
       <c r="B1719" t="s" s="2">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C1719" t="s" s="2">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="D1719" s="2"/>
     </row>
@@ -33139,24 +33136,12 @@
         <v>60</v>
       </c>
       <c r="B1720" t="s" s="2">
-        <v>3801</v>
+        <v>33</v>
       </c>
       <c r="C1720" t="s" s="2">
         <v>3802</v>
       </c>
       <c r="D1720" s="2"/>
-    </row>
-    <row r="1721">
-      <c r="A1721" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B1721" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="C1721" t="s" s="2">
-        <v>3803</v>
-      </c>
-      <c r="D1721" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
